--- a/output/pdf_financials_xlsx/HTRC.xlsx
+++ b/output/pdf_financials_xlsx/HTRC.xlsx
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.670855</v>
+        <v>-0.670855</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.390129</v>
+        <v>-0.390129</v>
       </c>
     </row>
     <row r="17">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.670855</v>
+        <v>-0.670855</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.390129</v>
+        <v>-0.390129</v>
       </c>
     </row>
     <row r="21">
@@ -834,10 +834,10 @@
         <v>-1.598237</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.670855</v>
+        <v>-0.670855</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.390129</v>
+        <v>-0.390129</v>
       </c>
     </row>
     <row r="24">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.670855</v>
+        <v>-0.670855</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.390129</v>
+        <v>-0.390129</v>
       </c>
     </row>
     <row r="28">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.670855</v>
+        <v>-0.670855</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.390129</v>
+        <v>-0.390129</v>
       </c>
     </row>
     <row r="30">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4095,10 +4095,10 @@
         <v>1.598237</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.670855</v>
+        <v>-0.670855</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.390129</v>
+        <v>-0.390129</v>
       </c>
     </row>
     <row r="46">

--- a/output/pdf_financials_xlsx/HTRC.xlsx
+++ b/output/pdf_financials_xlsx/HTRC.xlsx
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00311</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.670855</v>
+        <v>-0.667745</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.390129</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.670855</v>
+        <v>-0.667745</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.390129</v>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.069255</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.084885</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00971</v>
       </c>
     </row>
     <row r="35">
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.069255</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.084885</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00971</v>
       </c>
     </row>
     <row r="37">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">

--- a/output/pdf_financials_xlsx/HTRC.xlsx
+++ b/output/pdf_financials_xlsx/HTRC.xlsx
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.602511</v>
+        <v>-0.478979</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.08205999999999999</v>
+        <v>0.463806</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.244265</v>
+        <v>0.244141</v>
       </c>
     </row>
     <row r="107">
@@ -3377,7 +3377,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>-0.478979</v>
       </c>
